--- a/src/src/main/webapp/portal/zkb/courseSchedule/APM_ZKB_Course_Schedule_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/courseSchedule/APM_ZKB_Course_Schedule_Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C220751A-B3D7-4F92-9490-3408E0B93DD0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A549F6E-2503-4994-9398-BD37F286FD8D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,7 +11,7 @@
     <sheet name="课程计划" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">课程计划!$N$1:$N$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">课程计划!$M$1:$M$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>课程ID</t>
   </si>
@@ -53,9 +53,6 @@
   </si>
   <si>
     <t>批次号</t>
-  </si>
-  <si>
-    <t>是否生效</t>
   </si>
   <si>
     <t>课程类型</t>
@@ -406,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="31" style="3" customWidth="1"/>
@@ -415,12 +412,11 @@
     <col min="7" max="9" width="31" style="3" customWidth="1"/>
     <col min="10" max="10" width="20.44140625" style="4" customWidth="1"/>
     <col min="11" max="11" width="31" style="3" customWidth="1"/>
-    <col min="12" max="12" width="22.109375" style="3" customWidth="1"/>
-    <col min="13" max="13" width="20.44140625" style="6" customWidth="1"/>
-    <col min="14" max="14" width="22.109375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="20.44140625" style="6" customWidth="1"/>
+    <col min="13" max="13" width="22.109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -437,7 +433,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -454,31 +450,25 @@
       <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:E1048576" xr:uid="{9FFE1F59-8C25-434E-912F-0F6574E60065}">
       <formula1>1</formula1>
       <formula2>72686</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M1048576 J2:J1048576 F2:F1048576" xr:uid="{B3B15526-3625-4C80-9F23-7BD11B6E9148}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L1048576 J2:J1048576 F2:F1048576" xr:uid="{B3B15526-3625-4C80-9F23-7BD11B6E9148}">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L1048576" xr:uid="{6E5DC897-26FD-4F74-97BD-AC77EF6CFD55}">
-      <formula1>"是,否"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576" xr:uid="{F967C642-7937-476E-8118-0D5743D05F0C}">
-      <formula1>"线下,线上"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M1048576" xr:uid="{A73C7879-C8D9-41A9-B97E-3B8168E03C71}">
+      <formula1>"ATC,Online"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/src/main/webapp/portal/zkb/courseSchedule/APM_ZKB_Course_Schedule_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/courseSchedule/APM_ZKB_Course_Schedule_Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A549F6E-2503-4994-9398-BD37F286FD8D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAAA8167-A427-4F76-BA68-F80B59353545}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,7 +11,7 @@
     <sheet name="课程计划" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">课程计划!$M$1:$M$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">课程计划!$O$1:$O$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>课程ID</t>
   </si>
@@ -62,6 +62,15 @@
   </si>
   <si>
     <t>扣除名额</t>
+  </si>
+  <si>
+    <t>删除</t>
+  </si>
+  <si>
+    <t>开始培训时间</t>
+  </si>
+  <si>
+    <t>结束培训时间</t>
   </si>
 </sst>
 </file>
@@ -403,20 +412,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="31" style="3" customWidth="1"/>
-    <col min="4" max="5" width="22.77734375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="20.44140625" style="4" customWidth="1"/>
-    <col min="7" max="9" width="31" style="3" customWidth="1"/>
-    <col min="10" max="10" width="20.44140625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="31" style="3" customWidth="1"/>
-    <col min="12" max="12" width="20.44140625" style="6" customWidth="1"/>
-    <col min="13" max="13" width="22.109375" style="3" customWidth="1"/>
+    <col min="4" max="7" width="22.77734375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="20.44140625" style="4" customWidth="1"/>
+    <col min="9" max="11" width="31" style="3" customWidth="1"/>
+    <col min="12" max="12" width="20.44140625" style="4" customWidth="1"/>
+    <col min="13" max="13" width="31" style="3" customWidth="1"/>
+    <col min="14" max="14" width="20.44140625" style="6" customWidth="1"/>
+    <col min="15" max="15" width="22.109375" style="3" customWidth="1"/>
+    <col min="16" max="16" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -433,42 +443,54 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:E1048576" xr:uid="{9FFE1F59-8C25-434E-912F-0F6574E60065}">
+  <dataValidations count="4">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:G1048576" xr:uid="{9FFE1F59-8C25-434E-912F-0F6574E60065}">
       <formula1>1</formula1>
       <formula2>72686</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L1048576 J2:J1048576 F2:F1048576" xr:uid="{B3B15526-3625-4C80-9F23-7BD11B6E9148}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576 L2:L1048576 H2:H1048576" xr:uid="{B3B15526-3625-4C80-9F23-7BD11B6E9148}">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M1048576" xr:uid="{A73C7879-C8D9-41A9-B97E-3B8168E03C71}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576" xr:uid="{A73C7879-C8D9-41A9-B97E-3B8168E03C71}">
       <formula1>"ATC,Online"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576" xr:uid="{B7CBF9C6-1DD6-46DC-91EA-433D0FFC45A9}">
+      <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/src/main/webapp/portal/zkb/courseSchedule/APM_ZKB_Course_Schedule_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/courseSchedule/APM_ZKB_Course_Schedule_Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAAA8167-A427-4F76-BA68-F80B59353545}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF1BCD88-E137-4028-A796-EEE7E3190E43}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -477,12 +477,12 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:G1048576" xr:uid="{9FFE1F59-8C25-434E-912F-0F6574E60065}">
       <formula1>1</formula1>
       <formula2>72686</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576 L2:L1048576 H2:H1048576" xr:uid="{B3B15526-3625-4C80-9F23-7BD11B6E9148}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576 L2:L1048576" xr:uid="{B3B15526-3625-4C80-9F23-7BD11B6E9148}">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
@@ -492,6 +492,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576" xr:uid="{B7CBF9C6-1DD6-46DC-91EA-433D0FFC45A9}">
       <formula1>"是,否"</formula1>
     </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576" xr:uid="{A7573EB5-6B33-4D8D-A200-4F2BA8B76A18}">
+      <formula1>0</formula1>
+      <formula2>999999999999</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
